--- a/Atribuicoes_Carreiras_Editais.xlsx
+++ b/Atribuicoes_Carreiras_Editais.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maiap\OneDrive\Desktop\Atribuições Cargos\Tabelas de Atribuições\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maiap\OneDrive\Desktop\Desenvolvimento\Estudo_Atribuicoes_PCSP_2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A87A041-9F10-4F2A-A650-E5B1612B89FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57CBE6F7-450A-4DA6-BD94-71C7E0E7F6CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{12B8B67E-6E0E-4BBB-ABC1-5946BED6C755}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$G$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$J$130</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="411">
   <si>
     <t>Carreira</t>
   </si>
@@ -678,6 +678,600 @@
   </si>
   <si>
     <t>Atendente de Necrotério Policial</t>
+  </si>
+  <si>
+    <t>Carreira_Inglês</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>Police Chief / Police Delegate</t>
+  </si>
+  <si>
+    <t>Police Clerk / Desk Officer</t>
+  </si>
+  <si>
+    <t>Police Investigator / Detective</t>
+  </si>
+  <si>
+    <t>Forensic Expert / Criminalist</t>
+  </si>
+  <si>
+    <t>Medical Examiner / Forensic Pathologist</t>
+  </si>
+  <si>
+    <t>Fingerprint Examiner / Dactyloscopist</t>
+  </si>
+  <si>
+    <t>Fingerprint Examiner Assistant</t>
+  </si>
+  <si>
+    <t>Police Telecommunications Agent / Dispatcher</t>
+  </si>
+  <si>
+    <t>Police Agent / Operative</t>
+  </si>
+  <si>
+    <t>Police Jailer</t>
+  </si>
+  <si>
+    <t>Forensic Photographer</t>
+  </si>
+  <si>
+    <t>Forensic Sketch Artist</t>
+  </si>
+  <si>
+    <t>Autopsy Assistant</t>
+  </si>
+  <si>
+    <t>Morgue Attendant</t>
+  </si>
+  <si>
+    <t>atribuicao_inglês</t>
+  </si>
+  <si>
+    <t>Carry a firearm, badge, and handcuffs</t>
+  </si>
+  <si>
+    <t>Always serve the general public with courtesy and efficiency, either in person or by phone</t>
+  </si>
+  <si>
+    <t>Draft police reports under the guidance of the Police Authority</t>
+  </si>
+  <si>
+    <t>Drive police vehicles</t>
+  </si>
+  <si>
+    <t>Execute investigative diligence and/or requisitions determined by the Police Authority, drafting the respective reports</t>
+  </si>
+  <si>
+    <t>Approach individuals suspected of committing offenses, conducting personal searches when necessary</t>
+  </si>
+  <si>
+    <t>Identify individuals, including by digital means, whenever such procedure is deemed necessary</t>
+  </si>
+  <si>
+    <t>Escort and present legally arrested individuals to the competent Police Authority or where designated</t>
+  </si>
+  <si>
+    <t>Assist the Police Authority in the formalization of judicial police acts</t>
+  </si>
+  <si>
+    <t>Operate Civil Police communication and data systems</t>
+  </si>
+  <si>
+    <t>Perform acts inherent to the management of judicial police activities</t>
+  </si>
+  <si>
+    <t>Preside over judicial police acts and criminal offense investigations, perform administrative police acts, and conduct specialized preventive policing</t>
+  </si>
+  <si>
+    <t>Preside over criminal investigations and related actions, including those provided for in the Criminal Procedure Code and special legislation</t>
+  </si>
+  <si>
+    <t>Carry a firearm and operate with potential exposure to high-risk situations</t>
+  </si>
+  <si>
+    <t>Mediate conflicts</t>
+  </si>
+  <si>
+    <t>Act as secretary in drafting police reports, detailed summaries of minor offenses (termos circunstanciados), in-flagrante arrest records, police inquiries, administrative proceedings, investigations, and other judicial police documents (physical, digital, and/or in IT systems), under the presidency of the Police Chief, in addition to the duties provided for in Portaria DGP-30/2012 and the Organic Law of the São Paulo State Police (Lei Complementar nº 207/1979)</t>
+  </si>
+  <si>
+    <t>Assume responsibility for bail amounts received and seized items</t>
+  </si>
+  <si>
+    <t>Drive motor vehicles</t>
+  </si>
+  <si>
+    <t>Comply with institutional and operational security measures</t>
+  </si>
+  <si>
+    <t>Act in police investigative procedures</t>
+  </si>
+  <si>
+    <t>Perform other duties of a police and administrative nature, as well as execute other assigned tasks</t>
+  </si>
+  <si>
+    <t>Carry a firearm as a member of the Civil Police (pursuant to Lei nº 10.826/2003, article 6, II)</t>
+  </si>
+  <si>
+    <t>Operate with potential exposure to high-risk situations</t>
+  </si>
+  <si>
+    <t>Conduct investigative diligence and specialized preventive policing</t>
+  </si>
+  <si>
+    <t>Comply with written or verbal requisitions pertaining to judicial police work issued by the Police Chief</t>
+  </si>
+  <si>
+    <t>Execute warrants</t>
+  </si>
+  <si>
+    <t>Draft police reports and other judicial police acts and documents</t>
+  </si>
+  <si>
+    <t>Escort prisoners</t>
+  </si>
+  <si>
+    <t>Conduct arrests, apprehensions of individuals, and seizures</t>
+  </si>
+  <si>
+    <t>Maintain the security of sites where civil police activities are conducted</t>
+  </si>
+  <si>
+    <t>Serve internal and external publics in the performance of police duties</t>
+  </si>
+  <si>
+    <t>Intervene at any time in criminal occurrences</t>
+  </si>
+  <si>
+    <t>Transport persons and property linked to police occurrences</t>
+  </si>
+  <si>
+    <t>Maintain, handle, and deploy firearms and less-lethal equipment</t>
+  </si>
+  <si>
+    <t>Execute other acts compatible with judicial and administrative police activities, under the presidency of the Police Chief</t>
+  </si>
+  <si>
+    <t>Perform other duties of a police and administrative nature, as well as execute other assigned tasks, in addition to the functions provided for in Portaria DGP-30/2012 and the Organic Law of the São Paulo State Police (Lei Complementar nº 207/1979)</t>
+  </si>
+  <si>
+    <t>Perform forensic examinations and analyses within criminalistics related to Physics, Chemistry, Forensic Biology, and other areas of scientific and technological knowledge</t>
+  </si>
+  <si>
+    <t>Analyze documents and objects at crime scenes of any nature to uncover evidence or collect traces, or in laboratories, aiming to provide clarifying evidence for police inquiries, administrative proceedings, and/or criminal judicial lawsuits</t>
+  </si>
+  <si>
+    <t>Analyze traces for criminal identification through dactyloscopy, chiroscopy, podoscopy, and/or other techniques, to substantiate procedures and establish evidence of authorship and/or materiality of criminal offenses</t>
+  </si>
+  <si>
+    <t>Comply with forensic requests pertinent to criminal investigations and judicial police duties regarding the application of criminalistics knowledge, including drafting and systematizing the corresponding forensic reports to provide objective evidence supporting investigations of criminal and administrative offenses</t>
+  </si>
+  <si>
+    <t>Examine material elements at crime scenes with priority; verify the integrity and/or non-tampering of the scene, assets, and objects submitted for forensic examination</t>
+  </si>
+  <si>
+    <t>Respond to occurrences involving victims of structural collapses, landslides, cave-ins, fires, disasters, terrorism, traffic accidents, and toxic agents (solid, liquid, and gaseous) with or without bodies at the scene, with subsequent collection of these agents for complementary testing; respond to diverse crime scenes involving direct contact with vectors of highly contagious diseases and toxic agents (physical, chemical, and/or biological agents)</t>
+  </si>
+  <si>
+    <t>Handle, collect, and analyze raw, contaminated, and/or putrefied biological materials in human and/or animal bodily fluids, as well as various environmental contaminants</t>
+  </si>
+  <si>
+    <t>Perform generic and/or specific testing on stains, human blood clots, crusts, seminal fluid, urine, feces, saliva, etc.</t>
+  </si>
+  <si>
+    <t>Handle and analyze psychoactive drugs (narcotics); analyze industrial products (known and/or unknown), waste, metallic, and non-metallic products</t>
+  </si>
+  <si>
+    <t>Perform physical and/or chemical analyses of organic and inorganic substances</t>
+  </si>
+  <si>
+    <t>Perform perinecroscopic examinations, handling cadavers</t>
+  </si>
+  <si>
+    <t>Perform examinations related to the exhumation of cadavers</t>
+  </si>
+  <si>
+    <t>Carry a firearm, badge, and drive police vehicles</t>
+  </si>
+  <si>
+    <t>Serve the general public</t>
+  </si>
+  <si>
+    <t>Survey crime scenes, draft sketches or schematic drawings, and conduct photographic surveys</t>
+  </si>
+  <si>
+    <t>Operate technological equipment applicable to the forensic field</t>
+  </si>
+  <si>
+    <t>Perform digital/computer forensic examinations</t>
+  </si>
+  <si>
+    <t>Execute autopsies or necroscopic examinations on humans, decomposed body parts, and skeletal remains</t>
+  </si>
+  <si>
+    <t>Perform forensic exhumation examinations</t>
+  </si>
+  <si>
+    <t>Collect biological samples from humans for complementary testing purposes</t>
+  </si>
+  <si>
+    <t>Perform forensic examinations of an anthropological nature</t>
+  </si>
+  <si>
+    <t>Perform direct and indirect forensic examinations on living individuals: bodily injuries, sexological, intoxication, toxicological, and other medical specialties</t>
+  </si>
+  <si>
+    <t>Accompany forensic teams to crime scenes when necessary, at the discretion of the requesting Police Chief</t>
+  </si>
+  <si>
+    <t>Maintain and safeguard the chain of custody</t>
+  </si>
+  <si>
+    <t>Operate with potential exposure to high-risk situations, in addition to the duties provided for in Portaria DGP-30/2012, Lei Complementar nº 207/1979, and Lei Complementar nº 756/1994</t>
+  </si>
+  <si>
+    <t>Study friction ridges on the palms, fingers, and soles of feet through dermal papillae to identify individuals</t>
+  </si>
+  <si>
+    <t>Manage the collection, analysis, research, and archiving of relevant documents, assisting the Police Chief, in addition to those duties described in Lei Complementar nº 207/1979 and Portaria DGP-30/2012 (...)</t>
+  </si>
+  <si>
+    <t>Plan, coordinate, and control the capture and search in automated databases for reading, comparing, and identifying friction ridge impressions</t>
+  </si>
+  <si>
+    <t>Insert questioned friction ridge fragments into automated databases, as well as perform image processing, searching, reading, comparing, and identifying standard ridge impressions</t>
+  </si>
+  <si>
+    <t>Search ten-print, single-print, palm print, footprint, and photographic collections, as well as systematically organize them</t>
+  </si>
+  <si>
+    <t>Conduct civil and criminal identification of individuals by searching civil and/or criminal databases, generating composite sketches, and performing fingerprint forensics at crime or disaster scenes, vehicles, objects, documents, and related items, requested by police and judicial authorities, resulting in the drafting of forensic fingerprint reports</t>
+  </si>
+  <si>
+    <t>Apply and develop scientific techniques and procedures for treating and recovering dermal or epidermal tissue from cadavers, reconstructing friction ridge impressions for identification purposes</t>
+  </si>
+  <si>
+    <t>Conduct the identification of cadavers in various states through post-mortem fingerprint forensics (necropapiloscopia)</t>
+  </si>
+  <si>
+    <t>Conduct searches for missing persons using friction ridge impressions</t>
+  </si>
+  <si>
+    <t>Attend crime scenes, perform latent print lifting techniques for subsequent localization, development, lifting, and transport of fingerprint, palm print, and footprint fragments from objects with different surfaces</t>
+  </si>
+  <si>
+    <t>Perform forensic analysis of human facial aging and rejuvenation projections for identification purposes</t>
+  </si>
+  <si>
+    <t>Perform technical photographic and macro-photographic work to support forensic fingerprint and post-mortem fingerprint reports</t>
+  </si>
+  <si>
+    <t>Execute fingerprint collection work for personal identification</t>
+  </si>
+  <si>
+    <t>Register and forward collected data for classification and research</t>
+  </si>
+  <si>
+    <t>Assist the police fingerprint expert (papiloscopista) in the performance of their duties</t>
+  </si>
+  <si>
+    <t>Assist in preparing procedures related to criminal and civil identification, collecting fingerprints from individuals (living or deceased), as well as palm print and footprint fragments or impressions</t>
+  </si>
+  <si>
+    <t>Collect prints at crime scenes and collaborate with the police fingerprint expert in analyzing obtained data for identification purposes and in drafting dactyloscopic formulas</t>
+  </si>
+  <si>
+    <t>In addition to the functions provided for in Portaria DGP-30/2012, pursuant to Annex V of this public notice, and Lei nº 207/1979 (Organic Law of the São Paulo State Police)</t>
+  </si>
+  <si>
+    <t>Perform transmission or reception tasks of information of any nature via wire, radio, electricity, optical means, or any other electromagnetic process</t>
+  </si>
+  <si>
+    <t>Among others related to or arising from them, in addition to those described in Lei Complementar nº 207/1979 and Portaria DGP-30/2012, pursuant to Annex V of this public notice</t>
+  </si>
+  <si>
+    <t>Drive police vehicles for diverse police and administrative operations, ensuring proper functioning, maintenance, and cleanliness, in addition to the functions established in Lei nº 207/1979 (Organic Law of the São Paulo State Police) and Portaria DGP-30/2012 (Annex V), regarding compliance with diligences and/or requisitions determined by the Police Authority within judicial police activities</t>
+  </si>
+  <si>
+    <t>DUTIES NOT FOUND</t>
+  </si>
+  <si>
+    <t>Photograph police occurrences at any type of crime scene with or without victims, including contact with contaminated materials (physical, chemical, and biological agents) and/or cadavers, as well as various incidents: structural collapses, landslides, cave-ins, fires, disasters, traffic accidents, robbery, theft, among others, and/or participate in laboratory forensics under the guidance of the Forensic Expert or Medical Examiner</t>
+  </si>
+  <si>
+    <t>Participate directly in forensic investigations under adverse weather conditions, at any time of day or night</t>
+  </si>
+  <si>
+    <t>Handle contaminated materials (syringes, stilettos, knives, weapons, etc.) for photographic preparation</t>
+  </si>
+  <si>
+    <t>Photograph cadavers, injuries, punctures, bloodstains, signs of assault, etc., as well as decomposed bodies and exhumations</t>
+  </si>
+  <si>
+    <t>Handle and photograph psychoactive and/or toxic substances (narcotics, chemical products, among others)</t>
+  </si>
+  <si>
+    <t>Develop and enlarge photographs using chemical substances</t>
+  </si>
+  <si>
+    <t>Handle digital photographic archives, photo editing, and respective electronic files</t>
+  </si>
+  <si>
+    <t>Edit forensic reports</t>
+  </si>
+  <si>
+    <t>Intervene in factual situations through the exercise of police power whenever conflict warrants it to safeguard the life, health, and property of citizens</t>
+  </si>
+  <si>
+    <t>Forward demands presented by superiors and citizens, inside and outside the police unit, in the exercise of investigative, technical, or judicial police duties</t>
+  </si>
+  <si>
+    <t>Draft schematic drawings of police incidents, examination pieces, and crime scenes (such as collapses, landslides, cave-ins, fires, disasters, traffic accidents) to create sketches, with or without victims, under the guidance of the Forensic Expert</t>
+  </si>
+  <si>
+    <t>Conduct visual recognition assessments (recognição visuográfica)</t>
+  </si>
+  <si>
+    <t>Reconstruct crime scenes in schematic drawings or sketches under the guidance of the Forensic Expert</t>
+  </si>
+  <si>
+    <t>Respond to crime scenes such as flooded areas, open sewers, and slums, leading to direct contact with elements carrying various contagious diseases and toxic agents (solid, liquid, and gaseous)</t>
+  </si>
+  <si>
+    <t>Handle contaminating materials in order to draft planimetric surveys</t>
+  </si>
+  <si>
+    <t>Interact with victims of crimes, disasters, bodies in a state of decay, as well as vectors carrying various contagious diseases</t>
+  </si>
+  <si>
+    <t>Carry a firearm and drive police vehicles</t>
+  </si>
+  <si>
+    <t>Identify cadavers</t>
+  </si>
+  <si>
+    <t>Handle cadavers to enable the observation of external injuries</t>
+  </si>
+  <si>
+    <t>Execute and monitor exhumations</t>
+  </si>
+  <si>
+    <t>Open cranial, thoracic, and abdominal cavities to enable the observation of internal injuries</t>
+  </si>
+  <si>
+    <t>Collect visceral samples for laboratory testing</t>
+  </si>
+  <si>
+    <t>Reconstruct cadavers by suturing parts</t>
+  </si>
+  <si>
+    <t>Clean instruments used in autopsies</t>
+  </si>
+  <si>
+    <t>Recover skeletal remains, decomposed remnants, and intact cadavers to meet legal requirements</t>
+  </si>
+  <si>
+    <t>Clean bones</t>
+  </si>
+  <si>
+    <t>Recover cadavers or parts of them (recent deaths, decomposed bodies, and/or skeletal remains) from crime scenes</t>
+  </si>
+  <si>
+    <t>Transport cadavers or parts of them to the morgue</t>
+  </si>
+  <si>
+    <t>Clean cadavers or parts of them and forward them for examinations</t>
+  </si>
+  <si>
+    <t>Maintain the cleanliness of the body transport vehicle</t>
+  </si>
+  <si>
+    <t>Take measures for the identification of cadavers</t>
+  </si>
+  <si>
+    <t>Take measures for the burial of unclaimed cadavers</t>
+  </si>
+  <si>
+    <t>Handle clothes and objects from cadavers</t>
+  </si>
+  <si>
+    <t>Carry a firearm, badge, functional ID, and handcuffs</t>
+  </si>
+  <si>
+    <t>Serve the general public with courtesy and efficiency</t>
+  </si>
+  <si>
+    <t>Drive police vehicles and operate institutional communication systems</t>
+  </si>
+  <si>
+    <t>Execute other tasks related to the performance of duties</t>
+  </si>
+  <si>
+    <t>Reduzida_Inglês</t>
+  </si>
+  <si>
+    <t>Serve the general public with courtesy and efficiency, in person or by phone</t>
+  </si>
+  <si>
+    <t>Execute investigative diligence and requests from the Police Authority, drafting the respective reports</t>
+  </si>
+  <si>
+    <t>Approach individuals suspected of offenses, conducting personal searches when necessary</t>
+  </si>
+  <si>
+    <t>Identify individuals, including by digital means, when necessary</t>
+  </si>
+  <si>
+    <t>Escort and present legally arrested individuals to the competent Police Authority</t>
+  </si>
+  <si>
+    <t>Assist the Police Authority in formalizing judicial police acts</t>
+  </si>
+  <si>
+    <t>Judicial police management</t>
+  </si>
+  <si>
+    <t>Preside over criminal investigations</t>
+  </si>
+  <si>
+    <t>Preside over judicial police acts</t>
+  </si>
+  <si>
+    <t>Act as secretary for judicial police acts and criminal inquiries</t>
+  </si>
+  <si>
+    <t>Assume responsibility for seized items</t>
+  </si>
+  <si>
+    <t>Comply with institutional security measures</t>
+  </si>
+  <si>
+    <t>Act in criminal investigations</t>
+  </si>
+  <si>
+    <t>Specialized investigative diligence and crime prevention</t>
+  </si>
+  <si>
+    <t>Conduct arrests</t>
+  </si>
+  <si>
+    <t>Maintain security at judicial police sites</t>
+  </si>
+  <si>
+    <t>Intervene in police occurrences</t>
+  </si>
+  <si>
+    <t>Handle firearms and less-lethal weapons</t>
+  </si>
+  <si>
+    <t>Perform examinations using natural sciences</t>
+  </si>
+  <si>
+    <t>Analyze evidence at crime scenes or in laboratories</t>
+  </si>
+  <si>
+    <t>Analyze friction ridge evidence lato sensu</t>
+  </si>
+  <si>
+    <t>Comply with forensic science and criminalistics requisitions</t>
+  </si>
+  <si>
+    <t>Examine crime scenes</t>
+  </si>
+  <si>
+    <t>Respond to disaster occurrences</t>
+  </si>
+  <si>
+    <t>Handle biological materials</t>
+  </si>
+  <si>
+    <t>Perform testing on stains</t>
+  </si>
+  <si>
+    <t>Analyze psychoactive drugs</t>
+  </si>
+  <si>
+    <t>Analyze organic and inorganic substances</t>
+  </si>
+  <si>
+    <t>Perform perinecroscopic examinations (scene of death body inspection)</t>
+  </si>
+  <si>
+    <t>Survey crime scenes using sketches and photographs</t>
+  </si>
+  <si>
+    <t>Operate forensic equipment</t>
+  </si>
+  <si>
+    <t>Perform digital and computer forensics</t>
+  </si>
+  <si>
+    <t>Execute autopsies and necroscopic examinations</t>
+  </si>
+  <si>
+    <t>Perform forensic anthropology examinations</t>
+  </si>
+  <si>
+    <t>Perform forensic examinations on living individuals</t>
+  </si>
+  <si>
+    <t>Study fingerprint and friction ridge identification (fingerprint science)</t>
+  </si>
+  <si>
+    <t>Insert fingerprints into databases</t>
+  </si>
+  <si>
+    <t>Process fingerprints in computerized systems</t>
+  </si>
+  <si>
+    <t>Search fingerprint and biometric databases</t>
+  </si>
+  <si>
+    <t>Conduct civil and criminal identification using fingerprint forensics</t>
+  </si>
+  <si>
+    <t>Perform post-mortem fingerprint identification</t>
+  </si>
+  <si>
+    <t>Conduct fingerprint tracking for missing persons</t>
+  </si>
+  <si>
+    <t>Perform facial aging and rejuvenation forecasting</t>
+  </si>
+  <si>
+    <t>Capture digital/electronic fingerprints</t>
+  </si>
+  <si>
+    <t>Register and forward fingerprint classification data</t>
+  </si>
+  <si>
+    <t>Assist the fingerprint expert</t>
+  </si>
+  <si>
+    <t>Photograph diverse occurrences for the Superintendency of Technical-Scientific Police (SPTC)</t>
+  </si>
+  <si>
+    <t>Assist SPTC forensic experts</t>
+  </si>
+  <si>
+    <t>Handle and photograph psychoactive drugs</t>
+  </si>
+  <si>
+    <t>Process and edit any type of forensic photography for the SPTC</t>
+  </si>
+  <si>
+    <t>Conduct visual crime scene recognition assessments</t>
+  </si>
+  <si>
+    <t>Identify cadavers lato sensu</t>
+  </si>
+  <si>
+    <t>Handle cadavers in laboratory settings</t>
+  </si>
+  <si>
+    <t>Handle and manipulate cadavers lato sensu</t>
+  </si>
+  <si>
+    <t>Handle skeletal remains and body parts</t>
+  </si>
+  <si>
+    <t>Handle cadavers at crime scenes</t>
+  </si>
+  <si>
+    <t>Transport cadavers or body parts</t>
+  </si>
+  <si>
+    <t>Clean cadavers</t>
+  </si>
+  <si>
+    <t>Take measures for the burial of unclaimed bodies</t>
+  </si>
+  <si>
+    <t>Handle personal effects and objects from cadavers</t>
   </si>
 </sst>
 </file>
@@ -1090,3008 +1684,4181 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B223857B-A23A-4350-9B87-DEF8C406C531}">
-  <dimension ref="A1:G130"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.88671875" style="1"/>
-    <col min="4" max="4" width="27.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.33203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="I1" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D2" s="2">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="I2" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D3" s="2">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I3" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D4" s="2">
         <v>3</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I4" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D5" s="2">
         <v>4</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="I5" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D6" s="2">
         <v>5</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="I6" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D7" s="2">
         <v>6</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="I7" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D8" s="2">
         <v>7</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="I8" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D9" s="2">
         <v>8</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I9" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D10" s="2">
         <v>9</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I10" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D11" s="2">
         <v>10</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="H11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I11" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>2023</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D12" s="2">
         <v>1</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F12" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="I12" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>2023</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D13" s="2">
         <v>2</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F13" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="I13" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>2023</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D14" s="2">
         <v>3</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F14" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I14" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>2023</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D15" s="2">
         <v>4</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="F15" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="H15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>2023</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D16" s="2">
         <v>5</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F16" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="I16" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>2023</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D17" s="2">
         <v>1</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F17" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I17" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>2023</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D18" s="2">
         <v>2</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F18" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I18" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>2023</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D19" s="2">
         <v>3</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="F19" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F19" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="H19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>2023</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D20" s="2">
         <v>4</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F20" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I20" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>2023</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D21" s="2">
         <v>5</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F21" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="I21" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>2023</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D22" s="2">
         <v>6</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="F22" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="H22" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>2023</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D23" s="2">
         <v>7</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="F23" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="H23" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>2023</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D24" s="2">
         <v>8</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="F24" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="H24" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>2023</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D25" s="2">
         <v>1</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F25" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="I25" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>2023</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D26" s="2">
         <v>2</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="E26" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="F26" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="H26" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>2023</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D27" s="2">
         <v>3</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F27" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I27" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>2023</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="2">
+      <c r="C28" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D28" s="2">
         <v>4</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="F28" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G28" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F28" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="H28" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>2023</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D29" s="2">
         <v>5</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="E29" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="F29" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F29" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="H29" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>2023</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C30" s="2">
+      <c r="C30" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D30" s="2">
         <v>6</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="E30" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E30" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F30" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I30" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>2023</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D31" s="2">
         <v>7</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F31" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I31" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>2023</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C32" s="2">
+      <c r="C32" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D32" s="2">
         <v>8</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="E32" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="F32" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G32" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="H32" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>2023</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C33" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D33" s="2">
         <v>9</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="E33" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F33" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H33" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I33" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>2023</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D34" s="2">
         <v>10</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="E34" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="F34" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G34" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F34" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="H34" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>2023</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C35" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D35" s="2">
         <v>11</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="E35" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F35" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I35" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>2023</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C36" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D36" s="2">
         <v>12</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="E36" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E36" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F36" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G36" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="I36" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>2023</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D37" s="2">
         <v>13</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="E37" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="F37" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G37" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F37" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="H37" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>2023</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C38" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D38" s="2">
         <v>14</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="E38" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="F38" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G38" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F38" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="H38" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>2023</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C39" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D39" s="2">
         <v>15</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="E39" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="F39" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="G39" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F39" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="H39" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>2023</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="2">
+      <c r="C40" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D40" s="2">
         <v>16</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="E40" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="F40" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="G40" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F40" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="H40" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>2023</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="2">
+      <c r="C41" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D41" s="2">
         <v>1</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="E41" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F41" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H41" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="I41" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>2023</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="2">
+      <c r="C42" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D42" s="2">
         <v>2</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="E42" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F42" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H42" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="144" x14ac:dyDescent="0.3">
+      <c r="I42" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="144" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>2023</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C43" s="2">
+      <c r="C43" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D43" s="2">
         <v>3</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="E43" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F43" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H43" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="I43" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>2023</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C44" s="2">
+      <c r="C44" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D44" s="2">
         <v>4</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="E44" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F44" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H44" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="I44" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>2023</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C45" s="2">
+      <c r="C45" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D45" s="2">
         <v>5</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="E45" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F45" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H45" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="273.60000000000002" x14ac:dyDescent="0.3">
+      <c r="I45" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>2023</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C46" s="2">
+      <c r="C46" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D46" s="2">
         <v>6</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="E46" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E46" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F46" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H46" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="I46" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>2023</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C47" s="2">
+      <c r="C47" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D47" s="2">
         <v>7</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="E47" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F47" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H47" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="I47" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>2023</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C48" s="2">
+      <c r="C48" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D48" s="2">
         <v>8</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="E48" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F48" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H48" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="I48" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>2023</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C49" s="2">
+      <c r="C49" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D49" s="2">
         <v>9</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="E49" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F49" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H49" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I49" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>2023</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C50" s="2">
+      <c r="C50" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D50" s="2">
         <v>10</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="E50" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E50" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F50" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H50" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="G50" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I50" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>2023</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C51" s="2">
+      <c r="C51" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D51" s="2">
         <v>11</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="E51" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E51" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F51" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H51" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G51" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I51" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>2023</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C52" s="2">
+      <c r="C52" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D52" s="2">
         <v>12</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="E52" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F52" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H52" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I52" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>2023</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C53" s="2">
+      <c r="C53" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D53" s="2">
         <v>13</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="E53" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E53" s="3" t="s">
+      <c r="F53" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="G53" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F53" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="H53" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>2023</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C54" s="2">
+      <c r="C54" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D54" s="2">
         <v>14</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="E54" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E54" s="3" t="s">
+      <c r="F54" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="G54" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="H54" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>2023</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C55" s="2">
+      <c r="C55" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D55" s="2">
         <v>15</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="E55" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E55" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F55" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H55" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G55" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I55" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>2023</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C56" s="2">
+      <c r="C56" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D56" s="2">
         <v>16</v>
       </c>
-      <c r="D56" s="3" t="s">
+      <c r="E56" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E56" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F56" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H56" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="G56" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I56" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>2023</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C57" s="2">
+      <c r="C57" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D57" s="2">
         <v>17</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="E57" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E57" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F57" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H57" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="I57" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>2023</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C58" s="2">
+      <c r="C58" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D58" s="2">
         <v>1</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="E58" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F58" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H58" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I58" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>2023</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C59" s="2">
+      <c r="C59" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D59" s="2">
         <v>2</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="E59" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F59" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H59" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I59" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>2023</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C60" s="2">
+      <c r="C60" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D60" s="2">
         <v>3</v>
       </c>
-      <c r="D60" s="3" t="s">
+      <c r="E60" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E60" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F60" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H60" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I60" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>2023</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C61" s="2">
+      <c r="C61" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D61" s="2">
         <v>4</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="E61" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E61" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F61" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H61" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G61" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="I61" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>2023</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C62" s="2">
+      <c r="C62" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D62" s="2">
         <v>5</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="E62" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F62" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H62" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="I62" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>2023</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C63" s="2">
+      <c r="C63" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D63" s="2">
         <v>6</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="E63" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E63" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F63" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H63" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="G63" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I63" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>2023</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C64" s="2">
+      <c r="C64" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D64" s="2">
         <v>7</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="E64" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E64" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F64" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H64" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="G64" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I64" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>2023</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C65" s="2">
+      <c r="C65" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D65" s="2">
         <v>8</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="E65" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E65" s="3" t="s">
+      <c r="F65" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G65" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F65" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="H65" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>2023</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C66" s="2">
+      <c r="C66" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D66" s="2">
         <v>9</v>
       </c>
-      <c r="D66" s="3" t="s">
+      <c r="E66" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E66" s="3" t="s">
+      <c r="F66" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="G66" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="H66" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>2023</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C67" s="2">
+      <c r="C67" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D67" s="2">
         <v>10</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="E67" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="E67" s="3" t="s">
+      <c r="F67" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G67" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F67" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="H67" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>2017</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C68" s="2">
+      <c r="C68" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D68" s="2">
         <v>1</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="E68" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="E68" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F68" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H68" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G68" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="144" x14ac:dyDescent="0.3">
+      <c r="I68" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="144" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>2017</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C69" s="2">
+      <c r="C69" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D69" s="2">
         <v>2</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="E69" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="E69" s="3" t="s">
+      <c r="F69" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="G69" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F69" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="H69" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>2017</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C70" s="2">
+      <c r="C70" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D70" s="2">
         <v>3</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="E70" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E70" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F70" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H70" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="G70" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="I70" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>2017</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C71" s="2">
+      <c r="C71" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D71" s="2">
         <v>4</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="E71" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E71" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F71" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H71" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="G71" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="I71" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>2017</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C72" s="2">
+      <c r="C72" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D72" s="2">
         <v>5</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="E72" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F72" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H72" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="I72" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>2017</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C73" s="2">
+      <c r="C73" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D73" s="2">
         <v>6</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="E73" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E73" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F73" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H73" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="G73" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="I73" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>2017</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C74" s="2">
+      <c r="C74" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D74" s="2">
         <v>7</v>
       </c>
-      <c r="D74" s="3" t="s">
+      <c r="E74" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="E74" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F74" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H74" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="G74" s="3" t="s">
+      <c r="I74" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="J74" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>2017</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C75" s="2">
+      <c r="C75" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D75" s="2">
         <v>8</v>
       </c>
-      <c r="D75" s="3" t="s">
+      <c r="E75" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E75" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F75" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H75" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="G75" s="3" t="s">
+      <c r="I75" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="J75" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>2017</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C76" s="2">
+      <c r="C76" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D76" s="2">
         <v>9</v>
       </c>
-      <c r="D76" s="3" t="s">
+      <c r="E76" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="E76" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F76" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H76" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="I76" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>2017</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C77" s="2">
+      <c r="C77" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D77" s="2">
         <v>10</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="E77" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="E77" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F77" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H77" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="G77" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="I77" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>2017</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C78" s="2">
+      <c r="C78" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D78" s="2">
         <v>11</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="E78" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E78" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F78" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H78" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="G78" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="I78" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>2017</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C79" s="2">
+      <c r="C79" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D79" s="2">
         <v>12</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="E79" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E79" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F79" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H79" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G79" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="I79" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>2017</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C80" s="2">
+      <c r="C80" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D80" s="2">
         <v>1</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="E80" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="E80" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F80" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H80" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="G80" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="I80" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>2017</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C81" s="2">
+      <c r="C81" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D81" s="2">
         <v>2</v>
       </c>
-      <c r="D81" s="3" t="s">
+      <c r="E81" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="E81" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F81" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H81" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="G81" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="I81" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>2017</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C82" s="2">
+      <c r="C82" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D82" s="2">
         <v>3</v>
       </c>
-      <c r="D82" s="3" t="s">
+      <c r="E82" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="E82" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F82" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H82" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="G82" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="I82" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>2017</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C83" s="2">
+      <c r="C83" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D83" s="2">
         <v>4</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="E83" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F83" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H83" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="I83" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>2017</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C84" s="2">
+      <c r="C84" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D84" s="2">
         <v>5</v>
       </c>
-      <c r="D84" s="3" t="s">
+      <c r="E84" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E84" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F84" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H84" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G84" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="I84" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>2017</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C85" s="2">
+      <c r="C85" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D85" s="2">
         <v>6</v>
       </c>
-      <c r="D85" s="3" t="s">
+      <c r="E85" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="E85" s="3" t="s">
+      <c r="F85" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="G85" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F85" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G85" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="H85" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J85" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>2017</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="C86" s="2">
+      <c r="C86" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D86" s="2">
         <v>1</v>
       </c>
-      <c r="D86" s="3" t="s">
+      <c r="E86" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="E86" s="3" t="s">
+      <c r="F86" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="G86" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F86" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="H86" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>2017</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="C87" s="2">
+      <c r="C87" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D87" s="2">
         <v>2</v>
       </c>
-      <c r="D87" s="3" t="s">
+      <c r="E87" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E87" s="3" t="s">
+      <c r="F87" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="G87" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F87" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="H87" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J87" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>2017</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C88" s="2">
+      <c r="C88" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="D88" s="2">
         <v>1</v>
       </c>
-      <c r="D88" s="3" t="s">
+      <c r="E88" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E88" s="3" t="s">
+      <c r="F88" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="G88" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F88" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G88" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="H88" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>2017</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C89" s="2">
+      <c r="C89" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="D89" s="2">
         <v>2</v>
       </c>
-      <c r="D89" s="3" t="s">
+      <c r="E89" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E89" s="3" t="s">
+      <c r="F89" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="G89" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="H89" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>2024</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C90" s="2">
+      <c r="C90" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D90" s="2">
         <v>0</v>
       </c>
-      <c r="D90" s="3" t="s">
+      <c r="E90" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="E90" s="3" t="s">
+      <c r="F90" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="G90" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F90" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G90" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="H90" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J90" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
         <v>2013</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C91" s="2">
+      <c r="C91" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D91" s="2">
         <v>1</v>
       </c>
-      <c r="D91" s="3" t="s">
+      <c r="E91" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F91" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H91" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="I91" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>2013</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C92" s="2">
+      <c r="C92" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D92" s="2">
         <v>2</v>
       </c>
-      <c r="D92" s="3" t="s">
+      <c r="E92" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="E92" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F92" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H92" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G92" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="I92" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>2013</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C93" s="2">
+      <c r="C93" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D93" s="2">
         <v>3</v>
       </c>
-      <c r="D93" s="3" t="s">
+      <c r="E93" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E93" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F93" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H93" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G93" s="3" t="s">
+      <c r="I93" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="J93" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>2013</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C94" s="2">
+      <c r="C94" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D94" s="2">
         <v>4</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="E94" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F94" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H94" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G94" s="3" t="s">
+      <c r="I94" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="J94" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>2013</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C95" s="2">
+      <c r="C95" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D95" s="2">
         <v>5</v>
       </c>
-      <c r="D95" s="3" t="s">
+      <c r="E95" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E95" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F95" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H95" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="G95" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="I95" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="J95" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>2013</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C96" s="2">
+      <c r="C96" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D96" s="2">
         <v>6</v>
       </c>
-      <c r="D96" s="3" t="s">
+      <c r="E96" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F96" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H96" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="G96" s="3" t="s">
+      <c r="I96" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="J96" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
         <v>2013</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C97" s="2">
+      <c r="C97" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D97" s="2">
         <v>7</v>
       </c>
-      <c r="D97" s="3" t="s">
+      <c r="E97" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="E97" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F97" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H97" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="G97" s="3" t="s">
+      <c r="I97" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="J97" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>2013</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C98" s="2">
+      <c r="C98" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D98" s="2">
         <v>8</v>
       </c>
-      <c r="D98" s="3" t="s">
+      <c r="E98" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="E98" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F98" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H98" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="G98" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I98" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="J98" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
         <v>2013</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C99" s="2">
+      <c r="C99" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D99" s="2">
         <v>9</v>
       </c>
-      <c r="D99" s="3" t="s">
+      <c r="E99" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="E99" s="3" t="s">
+      <c r="F99" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G99" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F99" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G99" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="H99" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J99" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>2013</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C100" s="2">
+      <c r="C100" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D100" s="2">
         <v>10</v>
       </c>
-      <c r="D100" s="3" t="s">
+      <c r="E100" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="E100" s="3" t="s">
+      <c r="F100" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="G100" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="H100" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>2013</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C101" s="2">
+      <c r="C101" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D101" s="2">
         <v>1</v>
       </c>
-      <c r="D101" s="3" t="s">
+      <c r="E101" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F101" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H101" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="I101" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>2013</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C102" s="2">
+      <c r="C102" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D102" s="2">
         <v>2</v>
       </c>
-      <c r="D102" s="3" t="s">
+      <c r="E102" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="E102" s="3" t="s">
+      <c r="F102" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G102" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F102" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="H102" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
         <v>2013</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C103" s="2">
+      <c r="C103" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D103" s="2">
         <v>3</v>
       </c>
-      <c r="D103" s="3" t="s">
+      <c r="E103" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="E103" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F103" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H103" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G103" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="I103" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="J103" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
         <v>2013</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C104" s="2">
+      <c r="C104" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D104" s="2">
         <v>4</v>
       </c>
-      <c r="D104" s="3" t="s">
+      <c r="E104" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="E104" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F104" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H104" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="G104" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="I104" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="J104" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
         <v>2013</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C105" s="2">
+      <c r="C105" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D105" s="2">
         <v>5</v>
       </c>
-      <c r="D105" s="3" t="s">
+      <c r="E105" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="E105" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F105" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H105" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G105" s="3" t="s">
+      <c r="I105" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="J105" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
         <v>2013</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C106" s="2">
+      <c r="C106" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D106" s="2">
         <v>6</v>
       </c>
-      <c r="D106" s="3" t="s">
+      <c r="E106" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="E106" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F106" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H106" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G106" s="3" t="s">
+      <c r="I106" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="J106" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
         <v>2013</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C107" s="2">
+      <c r="C107" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D107" s="2">
         <v>7</v>
       </c>
-      <c r="D107" s="3" t="s">
+      <c r="E107" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="E107" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F107" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H107" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G107" s="3" t="s">
+      <c r="I107" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="J107" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
         <v>2013</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C108" s="2">
+      <c r="C108" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D108" s="2">
         <v>8</v>
       </c>
-      <c r="D108" s="3" t="s">
+      <c r="E108" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="E108" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F108" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H108" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G108" s="3" t="s">
+      <c r="I108" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="J108" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
         <v>2013</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C109" s="2">
+      <c r="C109" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D109" s="2">
         <v>9</v>
       </c>
-      <c r="D109" s="3" t="s">
+      <c r="E109" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="E109" s="3" t="s">
+      <c r="F109" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="G109" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F109" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G109" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="H109" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I109" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J109" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
         <v>2013</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C110" s="2">
+      <c r="C110" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D110" s="2">
         <v>10</v>
       </c>
-      <c r="D110" s="3" t="s">
+      <c r="E110" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E110" s="3" t="s">
+      <c r="F110" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="G110" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F110" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G110" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="H110" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J110" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
         <v>2013</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C111" s="2">
+      <c r="C111" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D111" s="2">
         <v>1</v>
       </c>
-      <c r="D111" s="3" t="s">
+      <c r="E111" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="E111" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F111" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H111" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G111" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="I111" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="J111" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
         <v>2013</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C112" s="2">
+      <c r="C112" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D112" s="2">
         <v>2</v>
       </c>
-      <c r="D112" s="3" t="s">
+      <c r="E112" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="E112" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F112" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H112" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="G112" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="I112" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="J112" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
         <v>2013</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C113" s="2">
+      <c r="C113" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D113" s="2">
         <v>3</v>
       </c>
-      <c r="D113" s="3" t="s">
+      <c r="E113" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="E113" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F113" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H113" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="G113" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="I113" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="J113" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
         <v>2013</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C114" s="2">
+      <c r="C114" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D114" s="2">
         <v>4</v>
       </c>
-      <c r="D114" s="3" t="s">
+      <c r="E114" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="E114" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F114" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H114" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="G114" s="3" t="s">
+      <c r="I114" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="J114" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
         <v>2013</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C115" s="2">
+      <c r="C115" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D115" s="2">
         <v>5</v>
       </c>
-      <c r="D115" s="3" t="s">
+      <c r="E115" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="E115" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F115" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H115" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="G115" s="3" t="s">
+      <c r="I115" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="J115" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
         <v>2013</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C116" s="2">
+      <c r="C116" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D116" s="2">
         <v>6</v>
       </c>
-      <c r="D116" s="3" t="s">
+      <c r="E116" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="E116" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F116" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H116" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="G116" s="3" t="s">
+      <c r="I116" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="J116" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
         <v>2013</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C117" s="2">
+      <c r="C117" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D117" s="2">
         <v>7</v>
       </c>
-      <c r="D117" s="3" t="s">
+      <c r="E117" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="E117" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F117" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H117" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="G117" s="3" t="s">
+      <c r="I117" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="J117" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
         <v>2013</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C118" s="2">
+      <c r="C118" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D118" s="2">
         <v>8</v>
       </c>
-      <c r="D118" s="3" t="s">
+      <c r="E118" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="E118" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F118" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H118" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="G118" s="3" t="s">
+      <c r="I118" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="J118" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
         <v>2013</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C119" s="2">
+      <c r="C119" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D119" s="2">
         <v>9</v>
       </c>
-      <c r="D119" s="3" t="s">
+      <c r="E119" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="E119" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F119" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H119" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="G119" s="3" t="s">
+      <c r="I119" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="J119" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
         <v>2013</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C120" s="2">
+      <c r="C120" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D120" s="2">
         <v>1</v>
       </c>
-      <c r="D120" s="3" t="s">
+      <c r="E120" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="E120" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F120" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H120" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="G120" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="I120" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="J120" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
         <v>2013</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C121" s="2">
+      <c r="C121" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D121" s="2">
         <v>2</v>
       </c>
-      <c r="D121" s="3" t="s">
+      <c r="E121" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="E121" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F121" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H121" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="G121" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="I121" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="J121" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
         <v>2013</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C122" s="2">
+      <c r="C122" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D122" s="2">
         <v>3</v>
       </c>
-      <c r="D122" s="3" t="s">
+      <c r="E122" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="E122" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F122" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H122" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="G122" s="3" t="s">
+      <c r="I122" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="J122" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
         <v>2013</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C123" s="2">
+      <c r="C123" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D123" s="2">
         <v>4</v>
       </c>
-      <c r="D123" s="3" t="s">
+      <c r="E123" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="E123" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F123" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H123" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="G123" s="3" t="s">
+      <c r="I123" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="J123" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
         <v>2013</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C124" s="2">
+      <c r="C124" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D124" s="2">
         <v>5</v>
       </c>
-      <c r="D124" s="3" t="s">
+      <c r="E124" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="E124" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F124" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H124" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="G124" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="I124" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="J124" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
         <v>2013</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C125" s="2">
+      <c r="C125" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D125" s="2">
         <v>6</v>
       </c>
-      <c r="D125" s="3" t="s">
+      <c r="E125" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E125" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F125" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H125" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="G125" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="I125" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="J125" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
         <v>2013</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C126" s="2">
+      <c r="C126" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D126" s="2">
         <v>7</v>
       </c>
-      <c r="D126" s="3" t="s">
+      <c r="E126" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E126" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F126" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H126" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G126" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="I126" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="J126" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
         <v>2013</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C127" s="2">
+      <c r="C127" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D127" s="2">
         <v>8</v>
       </c>
-      <c r="D127" s="3" t="s">
+      <c r="E127" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="E127" s="3" t="s">
+      <c r="F127" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="G127" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F127" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G127" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="H127" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I127" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J127" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
         <v>2013</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C128" s="2">
+      <c r="C128" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D128" s="2">
         <v>9</v>
       </c>
-      <c r="D128" s="3" t="s">
+      <c r="E128" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="E128" s="3" t="s">
+      <c r="F128" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="G128" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F128" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G128" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="H128" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I128" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J128" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
         <v>2013</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C129" s="2">
+      <c r="C129" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D129" s="2">
         <v>10</v>
       </c>
-      <c r="D129" s="3" t="s">
+      <c r="E129" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="E129" s="3" t="s">
+      <c r="F129" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="G129" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F129" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G129" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="H129" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I129" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J129" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
         <v>2013</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C130" s="2">
+      <c r="C130" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D130" s="2">
         <v>11</v>
       </c>
-      <c r="D130" s="3" t="s">
+      <c r="E130" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E130" s="3" t="s">
+      <c r="F130" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="G130" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F130" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G130" s="3" t="s">
+      <c r="H130" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I130" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J130" s="3" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G130" xr:uid="{B223857B-A23A-4350-9B87-DEF8C406C531}"/>
+  <autoFilter ref="A1:J130" xr:uid="{B223857B-A23A-4350-9B87-DEF8C406C531}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
